--- a/output/topology_excel/9099.xlsx
+++ b/output/topology_excel/9099.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,28 +490,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>121994</v>
+      </c>
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1008</v>
+        <v>411653</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>82</v>
+      </c>
+      <c r="J2" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -504,28 +528,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>122851</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6165</v>
+        <v>406117</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>84</v>
+      </c>
+      <c r="J3" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -533,28 +566,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>106040</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>943</v>
+        <v>411653</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>82</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -562,139 +604,184 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>106040</v>
+      </c>
+      <c r="D5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5253</v>
+        <v>406117</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>81</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>411653</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1066</v>
+        <v>58140</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>71</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>406117</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>168</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3819</v>
+        <v>57528</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>71</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>19685</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>972</v>
+        <v>39129</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>80</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>19558</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>104</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2560</v>
+        <v>38980</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>83</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -707,28 +794,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>411653</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>923</v>
+        <v>39129</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>86</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -736,28 +832,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>406117</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1709</v>
+        <v>38980</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>83</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -765,23 +870,32 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>411653</v>
+      </c>
+      <c r="D12" t="n">
+        <v>14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>852</v>
+        <v>14320</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>64</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -794,695 +908,911 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>406117</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1591</v>
+        <v>14499</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>64</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>121994</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1600</v>
+        <v>106040</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>340</v>
+      </c>
+      <c r="J14" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>121994</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>155</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3100</v>
+        <v>411653</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>102</v>
+      </c>
+      <c r="J15" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>121994</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>58140</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>204</v>
+      </c>
+      <c r="J16" t="n">
         <v>13</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1660</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>106040</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>154</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3080</v>
+        <v>106040</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>440</v>
+      </c>
+      <c r="J17" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>106040</v>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>12</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1118</v>
+        <v>411653</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>113</v>
+      </c>
+      <c r="J18" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>106040</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>277</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3731</v>
+        <v>19685</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>155</v>
+      </c>
+      <c r="J19" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>106040</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>996</v>
+        <v>122851</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>328</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>106040</v>
+      </c>
+      <c r="D21" t="n">
         <v>6</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>13</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>214</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2568</v>
+        <v>406117</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>100</v>
+      </c>
+      <c r="J21" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>106040</v>
+      </c>
+      <c r="D22" t="n">
+        <v>11</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>832</v>
+        <v>19558</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>154</v>
+      </c>
+      <c r="J22" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>106040</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>259</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3367</v>
+        <v>5913</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>63</v>
+      </c>
+      <c r="J23" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>122851</v>
+      </c>
+      <c r="D24" t="n">
         <v>6</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>14</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>768</v>
+        <v>406117</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>104</v>
+      </c>
+      <c r="J24" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>122851</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>260</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3120</v>
+        <v>57528</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>204</v>
+      </c>
+      <c r="J25" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>411653</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>340</v>
-      </c>
-      <c r="G26" t="n">
-        <v>4659</v>
+        <v>58140</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>398</v>
+      </c>
+      <c r="J26" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>411653</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>204</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2652</v>
+        <v>19685</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>94</v>
+      </c>
+      <c r="J27" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>411653</v>
+      </c>
+      <c r="D28" t="n">
+        <v>12</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>440</v>
-      </c>
-      <c r="G28" t="n">
-        <v>11000</v>
+        <v>39129</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>249</v>
+      </c>
+      <c r="J28" t="n">
+        <v>248</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
-      </c>
-      <c r="D29" t="inlineStr">
+        <v>411653</v>
+      </c>
+      <c r="D29" t="n">
+        <v>14</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F29" t="n">
-        <v>18</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3060</v>
+        <v>14320</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>192</v>
+      </c>
+      <c r="J29" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>411653</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>155</v>
-      </c>
-      <c r="G30" t="n">
-        <v>3565</v>
+        <v>406117</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>684</v>
+      </c>
+      <c r="J30" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>406117</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>328</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3936</v>
+        <v>57528</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>394</v>
+      </c>
+      <c r="J31" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>406117</v>
+      </c>
+      <c r="D32" t="n">
+        <v>11</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>19558</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>93</v>
+      </c>
+      <c r="J32" t="n">
         <v>3</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>11</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>154</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3542</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C33" t="n">
+        <v>406117</v>
+      </c>
+      <c r="D33" t="n">
         <v>13</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F33" t="n">
-        <v>20</v>
-      </c>
-      <c r="G33" t="n">
-        <v>3400</v>
+        <v>38980</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>247</v>
+      </c>
+      <c r="J33" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>406117</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>63</v>
-      </c>
-      <c r="G34" t="n">
-        <v>756</v>
+        <v>14499</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>191</v>
+      </c>
+      <c r="J34" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>58140</v>
+      </c>
+      <c r="D35" t="n">
+        <v>14</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>204</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2448</v>
+        <v>14320</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>179</v>
+      </c>
+      <c r="J35" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>57528</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>717</v>
-      </c>
-      <c r="G36" t="n">
-        <v>34614</v>
+        <v>14499</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>179</v>
+      </c>
+      <c r="J36" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1490,28 +1820,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>5913</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>457</v>
+        <v>19558</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>70</v>
+      </c>
+      <c r="J37" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1519,28 +1858,37 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>5913</v>
+      </c>
+      <c r="D38" t="n">
+        <v>13</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>13</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1222</v>
+        <v>38980</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>61</v>
+      </c>
+      <c r="J38" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1548,139 +1896,146 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>19685</v>
+      </c>
+      <c r="D39" t="n">
         <v>11</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" t="n">
-        <v>279</v>
+        <v>19558</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>127</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>15</v>
-      </c>
-      <c r="D40" t="inlineStr">
+        <v>19685</v>
+      </c>
+      <c r="D40" t="n">
+        <v>12</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F40" t="n">
-        <v>179</v>
-      </c>
-      <c r="G40" t="n">
-        <v>3580</v>
+        <v>39129</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>175</v>
+      </c>
+      <c r="J40" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>14</v>
-      </c>
-      <c r="D41" t="inlineStr">
+        <v>19558</v>
+      </c>
+      <c r="D41" t="n">
+        <v>13</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F41" t="n">
-        <v>179</v>
-      </c>
-      <c r="G41" t="n">
-        <v>3401</v>
+        <v>38980</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>174</v>
+      </c>
+      <c r="J41" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C42" t="n">
+        <v>39129</v>
+      </c>
+      <c r="D42" t="n">
         <v>13</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F42" t="n">
-        <v>61</v>
-      </c>
-      <c r="G42" t="n">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>6</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>9</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>12</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2964</v>
+        <v>38980</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>149</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/9099.xlsx
+++ b/output/topology_excel/9099.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1424,10 +1424,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>398</v>
+        <v>305</v>
       </c>
       <c r="J26" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1462,10 +1462,10 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="J27" t="n">
-        <v>82</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -1614,10 +1614,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>394</v>
+        <v>301</v>
       </c>
       <c r="J31" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -1633,15 +1633,15 @@
         <v>406117</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>19558</v>
+        <v>38980</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>93</v>
+        <v>247</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33">
@@ -1671,7 +1671,7 @@
         <v>406117</v>
       </c>
       <c r="D33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>38980</v>
+        <v>14499</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1690,26 +1690,26 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="J33" t="n">
-        <v>235</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>406117</v>
+        <v>58140</v>
       </c>
       <c r="D34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>14499</v>
+        <v>14320</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1728,15 +1728,15 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="J34" t="n">
-        <v>93</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>58140</v>
+        <v>57528</v>
       </c>
       <c r="D35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>14320</v>
+        <v>14499</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1769,31 +1769,31 @@
         <v>179</v>
       </c>
       <c r="J35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>57528</v>
+        <v>5913</v>
       </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>14499</v>
+        <v>19558</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1804,10 +1804,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="J36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -1823,15 +1823,15 @@
         <v>5913</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>19558</v>
+        <v>38980</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1842,15 +1842,15 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1858,18 +1858,18 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5913</v>
+        <v>19685</v>
       </c>
       <c r="D38" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>38980</v>
+        <v>19558</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="J38" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
@@ -1899,15 +1899,15 @@
         <v>19685</v>
       </c>
       <c r="D39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>19558</v>
+        <v>39129</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1918,15 +1918,15 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="J39" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>19685</v>
+        <v>19558</v>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>39129</v>
+        <v>38980</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J40" t="n">
         <v>65</v>
@@ -1964,15 +1964,15 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>19558</v>
+        <v>39129</v>
       </c>
       <c r="D41" t="n">
         <v>13</v>
@@ -1994,47 +1994,9 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="J41" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>12</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>39129</v>
-      </c>
-      <c r="D42" t="n">
-        <v>13</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>38980</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>149</v>
-      </c>
-      <c r="J42" t="n">
         <v>34</v>
       </c>
     </row>

--- a/output/topology_excel/9099.xlsx
+++ b/output/topology_excel/9099.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
         <v>12</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>340</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>204</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
         <v>13</v>
@@ -795,7 +795,7 @@
         <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>440</v>
+        <v>236</v>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -817,7 +817,7 @@
         <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>113</v>
+        <v>247</v>
       </c>
       <c r="F18" t="n">
-        <v>76</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>328</v>
+        <v>235</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>340</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,15 +938,15 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>63</v>
+        <v>204</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24" t="n">
         <v>6</v>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>104</v>
+        <v>440</v>
       </c>
       <c r="F24" t="n">
-        <v>98</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -993,7 +993,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,18 +1004,18 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>305</v>
+        <v>155</v>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>69</v>
+        <v>328</v>
       </c>
       <c r="F27" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>249</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>248</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="F29" t="n">
-        <v>93</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,18 +1092,18 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>684</v>
+        <v>63</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>301</v>
+        <v>104</v>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="F32" t="n">
-        <v>235</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="F33" t="n">
-        <v>93</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F34" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
@@ -1191,7 +1191,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,10 +1202,10 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="F35" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
@@ -1213,7 +1213,7 @@
         <v>9</v>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -1235,7 +1235,7 @@
         <v>9</v>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B38" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>127</v>
+        <v>214</v>
       </c>
       <c r="F38" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
@@ -1279,7 +1279,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F39" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="F40" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B41" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,10 +1334,340 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="F41" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>11</v>
+      </c>
+      <c r="B42" t="n">
+        <v>13</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>191</v>
+      </c>
+      <c r="F42" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>12</v>
+      </c>
+      <c r="B43" t="n">
+        <v>14</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>305</v>
+      </c>
+      <c r="F43" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>12</v>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>188</v>
+      </c>
+      <c r="F44" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>13</v>
+      </c>
+      <c r="B45" t="n">
+        <v>15</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>301</v>
+      </c>
+      <c r="F45" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>13</v>
+      </c>
+      <c r="B46" t="n">
+        <v>19</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>186</v>
+      </c>
+      <c r="F46" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>16</v>
+      </c>
+      <c r="B47" t="n">
+        <v>18</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>70</v>
+      </c>
+      <c r="F47" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>17</v>
+      </c>
+      <c r="B48" t="n">
+        <v>18</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>127</v>
+      </c>
+      <c r="F48" t="n">
         <v>34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>19</v>
+      </c>
+      <c r="B49" t="n">
+        <v>20</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>424</v>
+      </c>
+      <c r="F49" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="n">
+        <v>12</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>79</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" t="n">
+        <v>12</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>260</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" t="n">
+        <v>13</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>247</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" t="n">
+        <v>19</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>250</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>13</v>
+      </c>
+      <c r="B54" t="n">
+        <v>19</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>123</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>12</v>
+      </c>
+      <c r="B55" t="n">
+        <v>20</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>116</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" t="n">
+        <v>20</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>254</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/9099.xlsx
+++ b/output/topology_excel/9099.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,92 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Length_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Width_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Length_6</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Width_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Length_7</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Width_7</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Length_8</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Width_8</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Length_9</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Width_9</t>
         </is>
       </c>
     </row>
@@ -481,6 +561,22 @@
       <c r="F2" t="n">
         <v>40</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +599,22 @@
       <c r="F3" t="n">
         <v>39</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +637,22 @@
       <c r="F4" t="n">
         <v>13</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +675,22 @@
       <c r="F5" t="n">
         <v>12</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +713,22 @@
       <c r="F6" t="n">
         <v>13</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +751,22 @@
       <c r="F7" t="n">
         <v>12</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +789,22 @@
       <c r="F8" t="n">
         <v>20</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +827,22 @@
       <c r="F9" t="n">
         <v>20</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +865,22 @@
       <c r="F10" t="n">
         <v>13</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +903,22 @@
       <c r="F11" t="n">
         <v>12</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +941,22 @@
       <c r="F12" t="n">
         <v>13</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +979,22 @@
       <c r="F13" t="n">
         <v>12</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +1017,22 @@
       <c r="F14" t="n">
         <v>13</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +1055,22 @@
       <c r="F15" t="n">
         <v>18</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +1093,22 @@
       <c r="F16" t="n">
         <v>13</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +1131,22 @@
       <c r="F17" t="n">
         <v>21</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +1169,22 @@
       <c r="F18" t="n">
         <v>25</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +1207,22 @@
       <c r="F19" t="n">
         <v>13</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +1245,22 @@
       <c r="F20" t="n">
         <v>21</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -897,8 +1281,24 @@
         <v>340</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -919,8 +1319,24 @@
         <v>102</v>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1359,22 @@
       <c r="F23" t="n">
         <v>13</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1397,22 @@
       <c r="F24" t="n">
         <v>25</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1435,22 @@
       <c r="F25" t="n">
         <v>13</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1473,22 @@
       <c r="F26" t="n">
         <v>23</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1511,22 @@
       <c r="F27" t="n">
         <v>12</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1549,22 @@
       <c r="F28" t="n">
         <v>12</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1587,22 @@
       <c r="F29" t="n">
         <v>23</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1625,22 @@
       <c r="F30" t="n">
         <v>12</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1111,13 +1655,61 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>12</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>12</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>12</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>12</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>12</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>96</v>
+      </c>
+      <c r="V31" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1141,6 +1733,22 @@
       <c r="F32" t="n">
         <v>12</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1771,22 @@
       <c r="F33" t="n">
         <v>13</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1177,14 +1801,34 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="F34" t="n">
-        <v>65</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G34" t="n">
+        <v>155</v>
+      </c>
+      <c r="H34" t="n">
+        <v>20</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1851,22 @@
       <c r="F35" t="n">
         <v>34</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1889,22 @@
       <c r="F36" t="n">
         <v>12</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1243,14 +1919,34 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="F37" t="n">
-        <v>65</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G37" t="n">
+        <v>154</v>
+      </c>
+      <c r="H37" t="n">
+        <v>20</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1969,22 @@
       <c r="F38" t="n">
         <v>12</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +2007,22 @@
       <c r="F39" t="n">
         <v>20</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1309,14 +2037,34 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="F40" t="n">
-        <v>93</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G40" t="n">
+        <v>179</v>
+      </c>
+      <c r="H40" t="n">
+        <v>13</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +2087,22 @@
       <c r="F41" t="n">
         <v>19</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1353,14 +2117,34 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="F42" t="n">
-        <v>93</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G42" t="n">
+        <v>179</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1375,14 +2159,34 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="F43" t="n">
-        <v>25</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G43" t="n">
+        <v>20</v>
+      </c>
+      <c r="H43" t="n">
+        <v>12</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +2209,22 @@
       <c r="F44" t="n">
         <v>12</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1419,14 +2239,34 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="F45" t="n">
-        <v>25</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G45" t="n">
+        <v>19</v>
+      </c>
+      <c r="H45" t="n">
+        <v>13</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +2289,22 @@
       <c r="F46" t="n">
         <v>13</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +2327,22 @@
       <c r="F47" t="n">
         <v>20</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +2365,22 @@
       <c r="F48" t="n">
         <v>34</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +2403,22 @@
       <c r="F49" t="n">
         <v>25</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +2441,22 @@
       <c r="F50" t="n">
         <v>1</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +2479,22 @@
       <c r="F51" t="n">
         <v>1</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +2517,22 @@
       <c r="F52" t="n">
         <v>1</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +2555,22 @@
       <c r="F53" t="n">
         <v>1</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +2593,22 @@
       <c r="F54" t="n">
         <v>2</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +2631,22 @@
       <c r="F55" t="n">
         <v>5</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +2669,22 @@
       <c r="F56" t="n">
         <v>1</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
